--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484556_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484556_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2317</v>
+        <v>5.541</v>
       </c>
       <c r="E2" t="n">
-        <v>4.081</v>
+        <v>3.9849</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1507</v>
+        <v>1.5561</v>
       </c>
       <c r="G2" t="n">
         <v>4.062</v>
@@ -610,13 +610,13 @@
         <v>2.3823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9075</v>
+        <v>0.2168</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1267</v>
+        <v>0.0306</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7808</v>
+        <v>0.1862</v>
       </c>
       <c r="V2" t="n">
         <v>0.7125</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6792</v>
+        <v>2.7724</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5363</v>
+        <v>1.7286</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1428</v>
+        <v>1.0437</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0557</v>
@@ -688,13 +688,13 @@
         <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1385</v>
+        <v>-0.0453</v>
       </c>
       <c r="T3" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.2836</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2297</v>
+        <v>-0.3288</v>
       </c>
       <c r="V3" t="n">
         <v>1.7738</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3159</v>
+        <v>1.9066</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5853</v>
+        <v>1.2007</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7307</v>
+        <v>0.7059</v>
       </c>
       <c r="G4" t="n">
         <v>2.1658</v>
@@ -766,13 +766,13 @@
         <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2768</v>
+        <v>-0.1325</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1267</v>
+        <v>-0.2579</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1501</v>
+        <v>0.1254</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1267</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7688</v>
+        <v>1.7391</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3106</v>
+        <v>1.9836</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.2445</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9641999999999999</v>
@@ -844,13 +844,13 @@
         <v>2.7489</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7075</v>
+        <v>-0.7372</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5694</v>
+        <v>0.1037</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1382</v>
+        <v>-0.8409</v>
       </c>
       <c r="V5" t="n">
         <v>0.6916</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3862</v>
+        <v>0.8726</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7238</v>
+        <v>2.6853</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.11</v>
+        <v>-1.8127</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6146</v>
@@ -922,13 +922,13 @@
         <v>2.1991</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5612</v>
+        <v>-0.3024</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7345</v>
+        <v>0.227</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8267</v>
+        <v>-0.5294</v>
       </c>
       <c r="V6" t="n">
         <v>0.5068</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6047</v>
+        <v>-0.7752</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.32</v>
+        <v>-1.4162</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7154</v>
+        <v>0.641</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9526</v>
@@ -1000,13 +1000,13 @@
         <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2076</v>
+        <v>0.0371</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6041</v>
+        <v>0.5079</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3965</v>
+        <v>-0.4708</v>
       </c>
       <c r="V7" t="n">
         <v>0.5068</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6719</v>
+        <v>-2.68</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9921</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.664</v>
+        <v>-2.6144</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2531</v>
@@ -1078,13 +1078,13 @@
         <v>2.0158</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5708</v>
+        <v>0.5626</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7014</v>
+        <v>0.6437</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1306</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2566</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2282</v>
+        <v>-3.0577</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2959</v>
+        <v>1.392</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.524</v>
+        <v>-4.4497</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0938</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4459</v>
+        <v>-0.2754</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0565</v>
+        <v>0.0396</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3894</v>
+        <v>-0.3151</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3219</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3485</v>
+        <v>-3.7113</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3777</v>
+        <v>0.0892</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7262</v>
+        <v>-3.8005</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6353</v>
@@ -1234,13 +1234,13 @@
         <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1149</v>
+        <v>-0.2479</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3643</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2494</v>
+        <v>-0.3237</v>
       </c>
       <c r="V10" t="n">
         <v>-2.6606</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1326</v>
+        <v>-3.984</v>
       </c>
       <c r="E11" t="n">
         <v>-2.294</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8386</v>
+        <v>-1.69</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0176</v>
@@ -1312,13 +1312,13 @@
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5065</v>
+        <v>-0.3578</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1116</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3949</v>
+        <v>-0.2462</v>
       </c>
       <c r="V11" t="n">
         <v>1.7738</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.376500000000001</v>
+        <v>-1.376499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.288700000000002</v>
+        <v>9.288499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.665</v>
+        <v>-10.6651</v>
       </c>
       <c r="G12" t="n">
         <v>-5.359099999999999</v>
@@ -1393,10 +1393,10 @@
         <v>-1.282</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5425</v>
+        <v>1.5424</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8245</v>
+        <v>-2.8244</v>
       </c>
       <c r="V12" t="n">
         <v>1.5995</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.3888</v>
+        <v>2.9265</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2213</v>
+        <v>3.3943</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1676</v>
+        <v>-0.4679</v>
       </c>
       <c r="G13" t="n">
         <v>2.1267</v>
@@ -1468,13 +1468,13 @@
         <v>2.5656</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5117</v>
+        <v>1.0494</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7451</v>
+        <v>0.9182</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.1312</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7156</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. REOS CAMPOS</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7497</v>
+        <v>1.9402</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3609</v>
+        <v>1.6833</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6112</v>
+        <v>0.2569</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5788</v>
+        <v>-0.9635</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9278999999999999</v>
+        <v>-0.6562</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6509</v>
+        <v>-0.3073</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5773</v>
+        <v>0.5174</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7339</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8433</v>
+        <v>-0.3713</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-1.4808</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.806</v>
+        <v>-1.5448</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1925</v>
+        <v>0.064</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.7489</v>
+        <v>0.733</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9163</v>
+        <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0193</v>
+        <v>0.2702</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.1818</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1045</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.9005</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5339</v>
+        <v>1.9005</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBAÑEZ</t>
+          <t>A. RUIZ FRAGUEIRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.3873</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9752999999999999</v>
+        <v>2.1791</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9752999999999999</v>
+        <v>-0.7518</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9752999999999999</v>
+        <v>-1.1847</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.6586</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.8729</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.7857</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-2.4104</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-2.0576</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.3528</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.3286</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.1797</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5276</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2878</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUÑOZ</t>
+          <t>M. REOS CAMPOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6502</v>
+        <v>1.3767</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6502</v>
+        <v>1.8801</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.5034</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6502</v>
+        <v>1.5788</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6502</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.6509</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6502</v>
+        <v>2.5773</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6502</v>
+        <v>1.7339</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.8433</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.806</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.1925</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.6463</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.434</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.2123</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>M. BERENGUER CASCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.642</v>
+        <v>1.2837</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9141</v>
+        <v>1.9049</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.272</v>
+        <v>-0.6212</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9635</v>
+        <v>1.0511</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6562</v>
+        <v>-1.6902</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3073</v>
+        <v>2.7413</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5174</v>
+        <v>2.4833</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8885999999999999</v>
+        <v>-1.6045</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3713</v>
+        <v>4.0879</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4808</v>
+        <v>-1.4323</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5448</v>
+        <v>-0.0857</v>
       </c>
       <c r="O17" t="n">
-        <v>0.064</v>
+        <v>-1.3466</v>
       </c>
       <c r="P17" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6493</v>
+        <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.028</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5875</v>
+        <v>0.1991</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4405</v>
+        <v>-0.1122</v>
       </c>
       <c r="V17" t="n">
-        <v>1.9005</v>
+        <v>-0.7706</v>
       </c>
       <c r="W17" t="n">
-        <v>1.9005</v>
+        <v>0.3219</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0925</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BERENGUER CASCO</t>
+          <t>A. ORTEGA IBAÑEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5101</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1356</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6254999999999999</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0511</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6902</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7413</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4833</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6045</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>4.0879</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4323</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0857</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3466</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6867</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5701000000000001</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1165</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7706</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RUIZ FRAGUEIRO</t>
+          <t>J. CARRERAS MUÑOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4767</v>
+        <v>0.6502</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6984</v>
+        <v>0.6502</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2217</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7518</v>
+        <v>0.6502</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1847</v>
+        <v>0.6502</v>
       </c>
       <c r="I19" t="n">
-        <v>0.433</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6586</v>
+        <v>0.6502</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8729</v>
+        <v>0.6502</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7857</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4104</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.0576</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3528</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1991</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.582</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3318</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2502</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5276</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2878</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1447</v>
+        <v>0.1695</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1447</v>
+        <v>0.1695</v>
       </c>
       <c r="G21" t="n">
         <v>0.1282</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2835</v>
+        <v>0.1127</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1262</v>
+        <v>2.4147</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4098</v>
+        <v>-2.302</v>
       </c>
       <c r="G22" t="n">
         <v>1.0719</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.4623</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1086</v>
+        <v>0.3971</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0426</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3219</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. DE LA IGLESIA SANTAMARIA</t>
+          <t>J. CARRERAS MUNOZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2842</v>
+        <v>-1.0301</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.142</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1422</v>
+        <v>-1.0397</v>
       </c>
       <c r="G23" t="n">
-        <v>2.4279</v>
+        <v>0.9699</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0943</v>
+        <v>1.1557</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3336</v>
+        <v>-0.1858</v>
       </c>
       <c r="J23" t="n">
-        <v>2.7365</v>
+        <v>2.0081</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2105</v>
+        <v>1.8732</v>
       </c>
       <c r="L23" t="n">
-        <v>1.526</v>
+        <v>0.1349</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3086</v>
+        <v>-1.0382</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1161</v>
+        <v>-0.7175</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1925</v>
+        <v>-0.3207</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.7489</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0078</v>
+        <v>-0.1833</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7866</v>
+        <v>-0.1659</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7944</v>
+        <v>-0.0174</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>I. DE LA IGLESIA SANTAMARIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2963</v>
+        <v>-1.0976</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2742</v>
+        <v>-0.4305</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0221</v>
+        <v>-0.6671</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6537</v>
+        <v>2.4279</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8331</v>
+        <v>1.0943</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1794</v>
+        <v>1.3336</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4401</v>
+        <v>2.7365</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5235</v>
+        <v>1.2105</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0833</v>
+        <v>1.526</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2136</v>
+        <v>-0.3086</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3097</v>
+        <v>-0.1161</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0961</v>
+        <v>-0.1925</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0995</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0158</v>
+        <v>-3.6651</v>
       </c>
       <c r="R24" t="n">
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9502</v>
+        <v>0.1787</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.4981</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0354</v>
+        <v>-0.3194</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5068</v>
+        <v>-0.9554</v>
       </c>
       <c r="W24" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.7602</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUNOZ</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8402</v>
+        <v>-1.8075</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.375</v>
+        <v>-1.9246</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4652</v>
+        <v>0.1171</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9699</v>
+        <v>-1.2992</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1557</v>
+        <v>0.0503</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1858</v>
+        <v>-1.3495</v>
       </c>
       <c r="J25" t="n">
-        <v>2.0081</v>
+        <v>-1.0487</v>
       </c>
       <c r="K25" t="n">
-        <v>1.8732</v>
+        <v>0.1084</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1349</v>
+        <v>-1.157</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0382</v>
+        <v>-0.2505</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7175</v>
+        <v>-0.0581</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3207</v>
+        <v>-0.1925</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R25" t="n">
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.1146</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5505</v>
+        <v>0.0404</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4428</v>
+        <v>-0.155</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.267</v>
+        <v>-0.7602</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.267</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.316</v>
+        <v>-1.9125</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5454</v>
+        <v>-1.0434</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7705</v>
+        <v>-0.8691</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.278</v>
+        <v>-1.6537</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2619</v>
+        <v>-1.8331</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.0161</v>
+        <v>0.1794</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.197</v>
+        <v>-0.4401</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5977</v>
+        <v>-0.5235</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5994</v>
+        <v>0.0833</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.081</v>
+        <v>-1.2136</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3357</v>
+        <v>-1.3097</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.4167</v>
+        <v>0.0961</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2108</v>
+        <v>0.3339</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1652</v>
+        <v>0.1456</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0456</v>
+        <v>0.1883</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.6439</v>
+        <v>0.5068</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.6439</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.466</v>
+        <v>-1.9998</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.4054</v>
+        <v>-1.3531</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0606</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.2992</v>
+        <v>-1.278</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0503</v>
+        <v>-0.2619</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.3495</v>
+        <v>-1.0161</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.0487</v>
+        <v>-1.197</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1084</v>
+        <v>-0.5977</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.157</v>
+        <v>-0.5994</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2505</v>
+        <v>-0.081</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.0581</v>
+        <v>0.3357</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.1925</v>
+        <v>-0.4167</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.7732</v>
+        <v>0.1054</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4404</v>
+        <v>0.0272</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3327</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.7602</v>
+        <v>-0.6439</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.7602</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="28">
@@ -2593,22 +2593,22 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1.376399999999999</v>
+        <v>3.2997</v>
       </c>
       <c r="E28" t="n">
-        <v>10.6651</v>
+        <v>10.665</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.288500000000001</v>
+        <v>-7.3654</v>
       </c>
       <c r="G28" t="n">
-        <v>5.358899999999999</v>
+        <v>5.358900000000002</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7332000000000005</v>
+        <v>-0.7332000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>6.092099999999999</v>
+        <v>6.0921</v>
       </c>
       <c r="J28" t="n">
         <v>17.5882</v>
@@ -2626,25 +2626,25 @@
         <v>-7.4194</v>
       </c>
       <c r="O28" t="n">
-        <v>-4.809999999999999</v>
+        <v>-4.81</v>
       </c>
       <c r="P28" t="n">
-        <v>-3.665199999999999</v>
+        <v>-3.6652</v>
       </c>
       <c r="Q28" t="n">
-        <v>-18.3256</v>
+        <v>-18.32559999999999</v>
       </c>
       <c r="R28" t="n">
         <v>14.6606</v>
       </c>
       <c r="S28" t="n">
-        <v>1.2819</v>
+        <v>3.2051</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8244</v>
+        <v>2.8246</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.5423</v>
+        <v>0.3806000000000001</v>
       </c>
       <c r="V28" t="n">
         <v>-1.5992</v>
